--- a/a_materials/Lab Schedule.xlsx
+++ b/a_materials/Lab Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/IntroEconometrics/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626AC8AB-9A4A-0A4B-9077-4BFCEBF48524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060B4E65-20EA-7C46-9480-EFC38F08F73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{1103A02E-6F1A-EC41-B75E-F74E9889530B}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t xml:space="preserve">Lab </t>
   </si>
   <si>
-    <t>Midterm Exam Review</t>
-  </si>
-  <si>
     <t>R and R Markdown Overview</t>
   </si>
   <si>
@@ -79,10 +76,13 @@
     <t>RCTs + Regression Intro</t>
   </si>
   <si>
-    <t>Difference-in-Differences + RD</t>
-  </si>
-  <si>
     <t>Confidence Intervals, Hypothesis Testing and Regression Inference</t>
+  </si>
+  <si>
+    <t>Regression Discontinuity</t>
+  </si>
+  <si>
+    <t>Difference-in-Differences</t>
   </si>
 </sst>
 </file>
@@ -119,7 +119,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -127,16 +127,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -157,9 +175,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -197,7 +215,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -303,7 +321,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,7 +463,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -463,184 +481,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>46258</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <f>A2+7</f>
         <v>46265</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <f t="shared" ref="A4:A15" si="0">A3+7</f>
         <v>46272</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>46279</v>
+      </c>
+      <c r="B5" s="6">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>46286</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>46293</v>
+      </c>
+      <c r="B7" s="6">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>46300</v>
+      </c>
+      <c r="B8" s="6">
+        <v>7</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <f t="shared" si="0"/>
-        <v>46279</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <f t="shared" si="0"/>
-        <v>46286</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
-        <v>46293</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>46307</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
-        <v>46300</v>
-      </c>
-      <c r="B8" s="1">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>46314</v>
+      </c>
+      <c r="B10" s="6">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>46321</v>
+      </c>
+      <c r="B11" s="6">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>46328</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>46307</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>46314</v>
-      </c>
-      <c r="B10" s="1">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>46335</v>
+      </c>
+      <c r="B13" s="6">
+        <v>10</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>46342</v>
+      </c>
+      <c r="B14" s="6">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>46349</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>46321</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
-        <v>46328</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
-        <v>46335</v>
-      </c>
-      <c r="B13" s="1">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <f t="shared" si="0"/>
-        <v>46342</v>
-      </c>
-      <c r="B14" s="1">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <f t="shared" si="0"/>
-        <v>46349</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+      <c r="A16" s="5">
         <f>A15+7</f>
         <v>46356</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="6" t="s">
         <v>0</v>
       </c>
     </row>
